--- a/RF_simple/RF_simple_convesion.xlsx
+++ b/RF_simple/RF_simple_convesion.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="11784" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="11784"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet Data" sheetId="5" r:id="rId1"/>
